--- a/output/roomself_excel/11131.xlsx
+++ b/output/roomself_excel/11131.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>85250</v>
+        <v>183285</v>
       </c>
       <c r="D2" t="n">
-        <v>2340</v>
+        <v>3808</v>
       </c>
       <c r="E2" t="n">
-        <v>771</v>
+        <v>668</v>
       </c>
       <c r="F2" t="n">
-        <v>300</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38225</v>
+        <v>283536</v>
       </c>
       <c r="D3" t="n">
-        <v>1656</v>
+        <v>4292</v>
       </c>
       <c r="E3" t="n">
-        <v>139</v>
+        <v>592</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>536</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>572329</v>
+        <v>85250</v>
       </c>
       <c r="D4" t="n">
-        <v>9172</v>
+        <v>2340</v>
       </c>
       <c r="E4" t="n">
-        <v>991</v>
+        <v>334</v>
       </c>
       <c r="F4" t="n">
-        <v>903</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37620</v>
+        <v>218014</v>
       </c>
       <c r="D5" t="n">
-        <v>1556</v>
+        <v>4880</v>
       </c>
       <c r="E5" t="n">
-        <v>234</v>
+        <v>462</v>
       </c>
       <c r="F5" t="n">
-        <v>205</v>
+        <v>430</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32760</v>
+        <v>22472</v>
       </c>
       <c r="D6" t="n">
-        <v>1492</v>
+        <v>1272</v>
       </c>
       <c r="E6" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22472</v>
+        <v>31243</v>
       </c>
       <c r="D7" t="n">
-        <v>1272</v>
+        <v>1424</v>
       </c>
       <c r="E7" t="n">
-        <v>317</v>
+        <v>199</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>105450</v>
+        <v>13973</v>
       </c>
       <c r="D8" t="n">
-        <v>2620</v>
+        <v>984</v>
       </c>
       <c r="E8" t="n">
-        <v>824</v>
+        <v>89</v>
       </c>
       <c r="F8" t="n">
-        <v>253</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>43605</v>
+        <v>105508</v>
       </c>
       <c r="D9" t="n">
-        <v>1752</v>
+        <v>3808</v>
       </c>
       <c r="E9" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -642,17 +642,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>31243</v>
+        <v>43605</v>
       </c>
       <c r="D10" t="n">
-        <v>1424</v>
+        <v>1752</v>
       </c>
       <c r="E10" t="n">
-        <v>199</v>
+        <v>153</v>
       </c>
       <c r="F10" t="n">
         <v>25</v>
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>218014</v>
+        <v>140120</v>
       </c>
       <c r="D11" t="n">
-        <v>4880</v>
+        <v>3384</v>
       </c>
       <c r="E11" t="n">
-        <v>888</v>
+        <v>666</v>
       </c>
       <c r="F11" t="n">
-        <v>462</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19401</v>
+        <v>38225</v>
       </c>
       <c r="D12" t="n">
-        <v>1240</v>
+        <v>1656</v>
       </c>
       <c r="E12" t="n">
-        <v>223</v>
+        <v>139</v>
       </c>
       <c r="F12" t="n">
-        <v>178</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13973</v>
+        <v>37620</v>
       </c>
       <c r="D13" t="n">
-        <v>984</v>
+        <v>1556</v>
       </c>
       <c r="E13" t="n">
-        <v>89</v>
+        <v>234</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,64 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>140120</v>
+        <v>32760</v>
       </c>
       <c r="D14" t="n">
-        <v>3384</v>
+        <v>1492</v>
       </c>
       <c r="E14" t="n">
-        <v>666</v>
+        <v>193</v>
       </c>
       <c r="F14" t="n">
-        <v>250</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>105450</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2620</v>
+      </c>
+      <c r="E15" t="n">
+        <v>362</v>
+      </c>
+      <c r="F15" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>19401</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1240</v>
+      </c>
+      <c r="E16" t="n">
+        <v>215</v>
+      </c>
+      <c r="F16" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/11131.xlsx
+++ b/output/roomself_excel/11131.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>3808</v>
       </c>
-      <c r="E2" t="n">
-        <v>668</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>311</v>
-      </c>
+        <v>643</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>286</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,31 @@
       <c r="D3" t="n">
         <v>4292</v>
       </c>
-      <c r="E3" t="n">
-        <v>592</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>536</v>
-      </c>
+        <v>667</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>670</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +592,31 @@
       <c r="D4" t="n">
         <v>2340</v>
       </c>
-      <c r="E4" t="n">
-        <v>334</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>292</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="G4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>267</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +633,23 @@
       <c r="D5" t="n">
         <v>4880</v>
       </c>
-      <c r="E5" t="n">
-        <v>462</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>430</v>
-      </c>
+        <v>780</v>
+      </c>
+      <c r="G5" t="n">
+        <v>25</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +666,15 @@
       <c r="D6" t="n">
         <v>1272</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +691,23 @@
       <c r="D7" t="n">
         <v>1424</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>199</v>
       </c>
-      <c r="F7" t="n">
-        <v>25</v>
-      </c>
+      <c r="G7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +724,23 @@
       <c r="D8" t="n">
         <v>984</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>89</v>
       </c>
-      <c r="F8" t="n">
-        <v>25</v>
-      </c>
+      <c r="G8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +757,15 @@
       <c r="D9" t="n">
         <v>3808</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +782,23 @@
       <c r="D10" t="n">
         <v>1752</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>153</v>
       </c>
-      <c r="F10" t="n">
-        <v>25</v>
-      </c>
+      <c r="G10" t="n">
+        <v>25</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,11 +815,38 @@
       <c r="D11" t="n">
         <v>3384</v>
       </c>
-      <c r="E11" t="n">
-        <v>666</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>250</v>
+        <v>452</v>
+      </c>
+      <c r="G11" t="n">
+        <v>23</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>181</v>
+      </c>
+      <c r="J11" t="n">
+        <v>24</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>620</v>
+      </c>
+      <c r="M11" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -695,12 +864,23 @@
       <c r="D12" t="n">
         <v>1656</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>139</v>
       </c>
-      <c r="F12" t="n">
-        <v>25</v>
-      </c>
+      <c r="G12" t="n">
+        <v>25</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +897,31 @@
       <c r="D13" t="n">
         <v>1556</v>
       </c>
-      <c r="E13" t="n">
-        <v>234</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>205</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="G13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>180</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +938,23 @@
       <c r="D14" t="n">
         <v>1492</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>193</v>
       </c>
-      <c r="F14" t="n">
-        <v>25</v>
-      </c>
+      <c r="G14" t="n">
+        <v>25</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +971,23 @@
       <c r="D15" t="n">
         <v>2620</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>362</v>
       </c>
-      <c r="F15" t="n">
-        <v>25</v>
-      </c>
+      <c r="G15" t="n">
+        <v>25</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1004,23 @@
       <c r="D16" t="n">
         <v>1240</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>215</v>
       </c>
-      <c r="F16" t="n">
-        <v>25</v>
-      </c>
+      <c r="G16" t="n">
+        <v>25</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
